--- a/tests/fixtures/17_excel_template_invoice/17_excel_template_invoice_pattern-from-draft.xlsx
+++ b/tests/fixtures/17_excel_template_invoice/17_excel_template_invoice_pattern-from-draft.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -468,25 +468,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>read.direction</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pattern.version</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -496,12 +492,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>read.direction</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="D2" s="1" t="n"/>
@@ -510,29 +506,25 @@
       <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>document_type</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>INVOICE</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>config:</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -542,7 +534,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>LINE_Description</t>
+          <t>document_type</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -552,7 +544,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>DESCRIPTION</t>
+          <t>INVOICE</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -567,7 +559,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LINE_QTY</t>
+          <t>LINE_Description</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -577,7 +569,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>QTY</t>
+          <t>DESCRIPTION</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
@@ -592,7 +584,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>LINE_UNIT_PRICE</t>
+          <t>LINE_QTY</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -602,7 +594,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>UNIT PRICE</t>
+          <t>QTY</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
@@ -617,7 +609,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>LINE_AMOUNT</t>
+          <t>LINE_UNIT_PRICE</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -627,7 +619,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>AMOUNT</t>
+          <t>UNIT PRICE</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -642,7 +634,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>THANK_YOU</t>
+          <t>LINE_AMOUNT</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -652,7 +644,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thank you for your business!</t>
+          <t>AMOUNT</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -667,7 +659,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
+          <t>THANK_YOU</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -677,7 +669,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SUBTOTAL</t>
+          <t>Thank you for your business!</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
@@ -692,7 +684,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>TAXRATE</t>
+          <t>SUBTOTAL</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -702,7 +694,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>TAX RATE</t>
+          <t>SUBTOTAL</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
@@ -717,7 +709,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TAX</t>
+          <t>TAXRATE</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -727,7 +719,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>TAX</t>
+          <t>TAX RATE</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -742,7 +734,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>TAX</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -752,7 +744,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>TAX</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -760,29 +752,29 @@
       <c r="G12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>vendor.name</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>.+</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>lbl:</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -792,17 +784,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>inv.number</t>
+          <t>vendor.name</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>.+</t>
         </is>
       </c>
       <c r="E14" s="3" t="n"/>
@@ -817,17 +809,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>inv.date</t>
+          <t>inv.number</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>\d+</t>
         </is>
       </c>
       <c r="E15" s="3" t="n"/>
@@ -842,17 +834,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>customer.id</t>
+          <t>inv.date</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>\d+</t>
+          <t>.*</t>
         </is>
       </c>
       <c r="E16" s="3" t="n"/>
@@ -867,17 +859,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>inv.terms</t>
+          <t>customer.id</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>\d+</t>
         </is>
       </c>
       <c r="E17" s="3" t="n"/>
@@ -892,7 +884,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>client.name</t>
+          <t>inv.terms</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -917,7 +909,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>client.company</t>
+          <t>client.name</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -942,7 +934,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>client.address</t>
+          <t>client.company</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -967,7 +959,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>client.phone</t>
+          <t>client.address</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -992,7 +984,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>client.email</t>
+          <t>client.phone</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1002,7 +994,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>.+@.+</t>
+          <t>.+</t>
         </is>
       </c>
       <c r="E22" s="3" t="n"/>
@@ -1017,7 +1009,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>line.description</t>
+          <t>client.email</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1027,7 +1019,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>.+</t>
+          <t>.+@.+</t>
         </is>
       </c>
       <c r="E23" s="3" t="n"/>
@@ -1042,17 +1034,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>line.qty</t>
+          <t>line.description</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>\d*</t>
+          <t>.+</t>
         </is>
       </c>
       <c r="E24" s="3" t="n"/>
@@ -1067,17 +1059,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>line.unit_price</t>
+          <t>line.qty</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>\d*</t>
         </is>
       </c>
       <c r="E25" s="3" t="n"/>
@@ -1092,7 +1084,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>line.amount</t>
+          <t>line.unit_price</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1117,7 +1109,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>inv.subtotal</t>
+          <t>line.amount</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1142,7 +1134,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>inv.tax_rate</t>
+          <t>inv.subtotal</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1167,7 +1159,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>inv.tax</t>
+          <t>inv.tax_rate</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1192,7 +1184,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>inv.total</t>
+          <t>inv.tax</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1210,44 +1202,52 @@
       <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>inv.total</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>cell:B2</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>vendor.name</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>cell:next</t>
+          <t>cell:B2</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>document_type</t>
+          <t>vendor.name</t>
         </is>
       </c>
       <c r="C33" s="5" t="n"/>
@@ -1259,12 +1259,12 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>cell:B8</t>
+          <t>cell:next</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>client.name</t>
+          <t>document_type</t>
         </is>
       </c>
       <c r="C34" s="5" t="n"/>
@@ -1276,12 +1276,12 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>cell:E8</t>
+          <t>cell:B8</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>inv.number</t>
+          <t>client.name</t>
         </is>
       </c>
       <c r="C35" s="5" t="n"/>
@@ -1293,12 +1293,12 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>cell:F8</t>
+          <t>cell:E8</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>inv.date</t>
+          <t>inv.number</t>
         </is>
       </c>
       <c r="C36" s="5" t="n"/>
@@ -1310,12 +1310,12 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>cell:B9</t>
+          <t>cell:F8</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>client.company</t>
+          <t>inv.date</t>
         </is>
       </c>
       <c r="C37" s="5" t="n"/>
@@ -1327,12 +1327,12 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>cell:B10</t>
+          <t>cell:B9</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>client.address</t>
+          <t>client.company</t>
         </is>
       </c>
       <c r="C38" s="5" t="n"/>
@@ -1344,12 +1344,12 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>cell:E11</t>
+          <t>cell:B10</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>customer.id</t>
+          <t>client.address</t>
         </is>
       </c>
       <c r="C39" s="5" t="n"/>
@@ -1361,12 +1361,12 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>cell:F11</t>
+          <t>cell:E11</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>inv.terms</t>
+          <t>customer.id</t>
         </is>
       </c>
       <c r="C40" s="5" t="n"/>
@@ -1378,12 +1378,12 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>cell:B12</t>
+          <t>cell:F11</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>client.phone</t>
+          <t>inv.terms</t>
         </is>
       </c>
       <c r="C41" s="5" t="n"/>
@@ -1395,12 +1395,12 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>cell:B13</t>
+          <t>cell:B12</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>client.email</t>
+          <t>client.phone</t>
         </is>
       </c>
       <c r="C42" s="5" t="n"/>
@@ -1410,147 +1410,131 @@
       <c r="G42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>cell:B13</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>client.email</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>table:1</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>LINE_Description</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>LINE_QTY</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>LINE_UNIT_PRICE</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>LINE_AMOUNT</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="7" t="n"/>
-      <c r="B45" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>SKIP_IF</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="n"/>
-      <c r="B46" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="n"/>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>DATA:{0,15}</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>line.description</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>line.qty</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>line.unit_price</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>line.amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n"/>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>FOOTER:1</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>THANK_YOU</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>SUBTOTAL</t>
-        </is>
-      </c>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>inv.subtotal</t>
         </is>
       </c>
     </row>
@@ -1563,17 +1547,17 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>THANK_YOU</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>TAXRATE</t>
+          <t>SUBTOTAL</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
@@ -1583,7 +1567,7 @@
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>inv.tax_rate</t>
+          <t>inv.subtotal</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1590,7 @@
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>TAX</t>
+          <t>TAXRATE</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
@@ -1616,7 +1600,7 @@
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>inv.tax</t>
+          <t>inv.tax_rate</t>
         </is>
       </c>
     </row>
@@ -1639,32 +1623,65 @@
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
+          <t>TAX</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>inv.tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n"/>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>FOOTER:1</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F50" s="1" t="inlineStr">
+      <c r="F51" s="1" t="inlineStr">
         <is>
           <t>IGNORE</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>inv.total</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
